--- a/data/gravel/Litespeed Toscano 2025.xlsx
+++ b/data/gravel/Litespeed Toscano 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3517EC-1B28-CB4A-ACD1-42429ECA134D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2FDCE4-AA90-3D4E-AC60-0655A40DD2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8440" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="132">
   <si>
     <t>brand</t>
   </si>
@@ -414,6 +414,21 @@
   </si>
   <si>
     <t>72.0°</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
   </si>
 </sst>
 </file>
@@ -781,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF69"/>
+  <dimension ref="A1:AF72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2539,10 +2554,10 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>30</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>70</v>
+        <v>127</v>
+      </c>
+      <c r="B35" t="s">
+        <v>128</v>
       </c>
       <c r="J35" s="6" t="s">
         <v>90</v>
@@ -2556,10 +2571,10 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>66</v>
+        <v>129</v>
+      </c>
+      <c r="B36" t="s">
+        <v>130</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
@@ -2567,7 +2582,10 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>131</v>
+      </c>
+      <c r="B37" t="s">
+        <v>120</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -2595,10 +2613,10 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38">
-        <v>48</v>
+        <v>30</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="E38">
         <f t="shared" ref="E38:H38" si="5">((622 + 2*E29)/2*COS(E10*PI()/180) - E17)/SIN(E10*PI()/180)</f>
@@ -2622,9 +2640,11 @@
     </row>
     <row r="39" spans="1:12" ht="21">
       <c r="A39" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="C39" s="2"/>
       <c r="J39" s="6" t="s">
         <v>95</v>
@@ -2638,7 +2658,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
@@ -2646,10 +2666,10 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>66</v>
+        <v>33</v>
+      </c>
+      <c r="B41">
+        <v>48</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>97</v>
@@ -2663,33 +2683,34 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>37</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B42" s="1"/>
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
       <c r="L42" s="6"/>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>102</v>
@@ -2697,119 +2718,113 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="C49" s="1"/>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50">
         <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" s="1"/>
+        <v>43</v>
+      </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>44</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>45</v>
+      </c>
+      <c r="B53">
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>49</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B54" s="1"/>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>50</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>103</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>51</v>
-      </c>
-      <c r="B56" s="1"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>54</v>
-      </c>
-      <c r="B59">
-        <v>2</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B59" s="1"/>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>55</v>
-      </c>
-      <c r="B60">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>58</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>66</v>
@@ -2817,7 +2832,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>66</v>
@@ -2825,23 +2840,23 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>61</v>
-      </c>
-      <c r="B66">
-        <v>2399</v>
+        <v>58</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>62</v>
-      </c>
-      <c r="B67">
-        <v>4975</v>
+        <v>59</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>66</v>
@@ -2849,19 +2864,38 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
+        <v>61</v>
+      </c>
+      <c r="B69">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>62</v>
+      </c>
+      <c r="B70">
+        <v>4975</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>63</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
         <v>64</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>67</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="K31:K32"/>
     <mergeCell ref="J41:J42"/>
     <mergeCell ref="K41:K42"/>
     <mergeCell ref="L29:L30"/>
@@ -2878,6 +2912,11 @@
     <mergeCell ref="J33:J34"/>
     <mergeCell ref="K33:K34"/>
     <mergeCell ref="J35:J36"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="K31:K32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Litespeed Toscano 2025.xlsx
+++ b/data/gravel/Litespeed Toscano 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2FDCE4-AA90-3D4E-AC60-0655A40DD2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827409C3-5B66-F844-B53A-C19CBC338797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="132">
   <si>
     <t>brand</t>
   </si>
@@ -2699,9 +2699,7 @@
       <c r="A44" t="s">
         <v>36</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="B44" s="1"/>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
@@ -2896,6 +2894,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="K31:K32"/>
     <mergeCell ref="J41:J42"/>
     <mergeCell ref="K41:K42"/>
     <mergeCell ref="L29:L30"/>
@@ -2912,11 +2915,6 @@
     <mergeCell ref="J33:J34"/>
     <mergeCell ref="K33:K34"/>
     <mergeCell ref="J35:J36"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="K31:K32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Litespeed Toscano 2025.xlsx
+++ b/data/gravel/Litespeed Toscano 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827409C3-5B66-F844-B53A-C19CBC338797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF954EF-1ED5-914B-A17E-553F3B1F9872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="133">
   <si>
     <t>brand</t>
   </si>
@@ -429,6 +429,9 @@
   </si>
   <si>
     <t>fork</t>
+  </si>
+  <si>
+    <t>https://litespeed.com/cdn/shop/files/toscano_8e8f560f-c8fc-40d8-b4ce-ba0aa1252195.png?v=1695761382</t>
   </si>
 </sst>
 </file>
@@ -842,6 +845,11 @@
         <v>125</v>
       </c>
     </row>
+    <row r="6" spans="1:32">
+      <c r="B6" t="s">
+        <v>132</v>
+      </c>
+    </row>
     <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>5</v>
@@ -2894,11 +2902,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="K31:K32"/>
     <mergeCell ref="J41:J42"/>
     <mergeCell ref="K41:K42"/>
     <mergeCell ref="L29:L30"/>
@@ -2915,6 +2918,11 @@
     <mergeCell ref="J33:J34"/>
     <mergeCell ref="K33:K34"/>
     <mergeCell ref="J35:J36"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="K31:K32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Litespeed Toscano 2025.xlsx
+++ b/data/gravel/Litespeed Toscano 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF954EF-1ED5-914B-A17E-553F3B1F9872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CF8579-7B69-E94B-A874-47D365C1DE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="135">
   <si>
     <t>brand</t>
   </si>
@@ -236,9 +236,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>frame_weight</t>
   </si>
   <si>
@@ -432,6 +429,15 @@
   </si>
   <si>
     <t>https://litespeed.com/cdn/shop/files/toscano_8e8f560f-c8fc-40d8-b4ce-ba0aa1252195.png?v=1695761382</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Chattanooga, Tennessee, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -799,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF72"/>
+  <dimension ref="A1:AF73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -810,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:32">
@@ -818,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -842,12 +848,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:32">
       <c r="B6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:32">
@@ -855,13 +861,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:32">
@@ -869,90 +875,90 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="K8" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="L8" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="S8" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="S8" s="4" t="s">
+      <c r="T8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="T8" s="4" t="s">
+      <c r="U8" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="U8" s="4" t="s">
+      <c r="V8" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="V8" s="4" t="s">
+      <c r="W8" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="W8" s="4" t="s">
+      <c r="X8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="X8" s="4" t="s">
+      <c r="Y8" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="Y8" s="4" t="s">
+      <c r="Z8" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="Z8" s="4" t="s">
+      <c r="AA8" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="AA8" s="4" t="s">
+      <c r="AB8" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="AB8" s="4" t="s">
+      <c r="AC8" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="AC8" s="4" t="s">
+      <c r="AD8" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="AD8" s="4" t="s">
+      <c r="AE8" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AE8" s="4" t="s">
+      <c r="AF8" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="AF8" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:32">
@@ -960,7 +966,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" s="5">
         <f>J9*10</f>
@@ -1006,16 +1012,16 @@
         <v>61</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R9" s="5">
         <v>51.7</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U9" s="5">
         <v>43</v>
@@ -1059,7 +1065,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" s="5">
         <f>VALUE(LEFT(J10,4))</f>
@@ -1087,34 +1093,34 @@
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R10" s="5">
         <v>53.2</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T10" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U10" s="5">
         <v>44.5</v>
@@ -1158,7 +1164,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C11" s="5">
         <f>VALUE(LEFT(J11,4))</f>
@@ -1186,34 +1192,34 @@
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q11" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q11" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="R11" s="5">
         <v>55.5</v>
       </c>
       <c r="S11" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U11" s="5">
         <v>47</v>
@@ -1257,7 +1263,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12" s="5">
         <f t="shared" ref="C12:C21" si="2">J12*10</f>
@@ -1303,16 +1309,16 @@
         <v>55</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R12" s="5">
         <v>56.8</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T12" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U12" s="5">
         <v>49.5</v>
@@ -1356,7 +1362,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13" s="5">
         <f t="shared" si="2"/>
@@ -1402,16 +1408,16 @@
         <v>43.5</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R13" s="5">
         <v>59</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U13" s="5">
         <v>52</v>
@@ -1455,7 +1461,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C14" s="5">
         <f t="shared" si="2"/>
@@ -1501,16 +1507,16 @@
         <v>6.8</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R14" s="5">
         <v>61</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T14" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U14" s="5">
         <v>55</v>
@@ -1554,7 +1560,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="5">
         <f t="shared" si="2"/>
@@ -1600,7 +1606,7 @@
         <v>108.3</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:32">
@@ -1608,7 +1614,7 @@
         <v>65</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C16" s="5">
         <f t="shared" si="2"/>
@@ -1655,49 +1661,49 @@
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="S16" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="S16" s="4" t="s">
+      <c r="T16" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="T16" s="4" t="s">
+      <c r="U16" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="U16" s="4" t="s">
+      <c r="V16" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="4" t="s">
+      <c r="W16" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="W16" s="4" t="s">
+      <c r="X16" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="X16" s="4" t="s">
+      <c r="Y16" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="Y16" s="4" t="s">
+      <c r="Z16" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="Z16" s="4" t="s">
+      <c r="AA16" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="AA16" s="4" t="s">
+      <c r="AB16" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="AB16" s="4" t="s">
+      <c r="AC16" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="AC16" s="4" t="s">
+      <c r="AD16" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="AD16" s="4" t="s">
+      <c r="AE16" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AE16" s="4" t="s">
+      <c r="AF16" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="AF16" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:32">
@@ -1705,7 +1711,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C17" s="5">
         <f t="shared" si="2"/>
@@ -1751,16 +1757,16 @@
         <v>5</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R17" s="5">
         <v>51.7</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T17" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U17" s="5">
         <v>43</v>
@@ -1804,7 +1810,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C18" s="5">
         <f t="shared" si="2"/>
@@ -1850,16 +1856,16 @@
         <v>84.5</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R18" s="5">
         <v>53.2</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U18" s="5">
         <v>44.5</v>
@@ -1903,7 +1909,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C19" s="5">
         <f t="shared" si="2"/>
@@ -1949,16 +1955,16 @@
         <v>20.5</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R19" s="5">
         <v>55.5</v>
       </c>
       <c r="S19" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T19" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U19" s="5">
         <v>47</v>
@@ -2002,7 +2008,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C20" s="5">
         <f t="shared" si="2"/>
@@ -2048,16 +2054,16 @@
         <v>64</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R20" s="5">
         <v>56.8</v>
       </c>
       <c r="S20" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T20" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U20" s="5">
         <v>49.5</v>
@@ -2101,7 +2107,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21" s="5">
         <f t="shared" si="2"/>
@@ -2147,16 +2153,16 @@
         <v>41.5</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R21" s="5">
         <v>59</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T21" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U21" s="5">
         <v>52</v>
@@ -2200,7 +2206,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C22" s="5">
         <v>80</v>
@@ -2240,16 +2246,16 @@
         <v>110</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R22" s="5">
         <v>61</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T22" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U22" s="5">
         <v>55</v>
@@ -2293,7 +2299,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23" s="5">
         <v>170</v>
@@ -2340,12 +2346,12 @@
     </row>
     <row r="25" spans="1:32">
       <c r="A25" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:32">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:32">
@@ -2399,13 +2405,13 @@
         <v>40</v>
       </c>
       <c r="J29" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="K29" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="L29" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:32">
@@ -2462,13 +2468,13 @@
         <v>188</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K31" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="L31" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:32">
@@ -2522,13 +2528,13 @@
         <v>188</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K33" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2562,27 +2568,27 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" t="s">
         <v>127</v>
       </c>
-      <c r="B35" t="s">
-        <v>128</v>
-      </c>
       <c r="J35" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K35" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="L35" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
+        <v>128</v>
+      </c>
+      <c r="B36" t="s">
         <v>129</v>
-      </c>
-      <c r="B36" t="s">
-        <v>130</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
@@ -2590,33 +2596,33 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K37" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="L37" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2624,7 +2630,7 @@
         <v>30</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E38">
         <f t="shared" ref="E38:H38" si="5">((622 + 2*E29)/2*COS(E10*PI()/180) - E17)/SIN(E10*PI()/180)</f>
@@ -2655,13 +2661,13 @@
       </c>
       <c r="C39" s="2"/>
       <c r="J39" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K39" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L39" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="L39" s="6" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2680,13 +2686,13 @@
         <v>48</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K41" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="L41" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="L41" s="6" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2719,7 +2725,7 @@
         <v>38</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2737,7 +2743,7 @@
         <v>41</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C49" s="1"/>
     </row>
@@ -2793,7 +2799,7 @@
         <v>50</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -2849,7 +2855,7 @@
         <v>58</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2897,11 +2903,24 @@
         <v>64</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>67</v>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>132</v>
+      </c>
+      <c r="B73" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="K31:K32"/>
     <mergeCell ref="J41:J42"/>
     <mergeCell ref="K41:K42"/>
     <mergeCell ref="L29:L30"/>
@@ -2918,11 +2937,6 @@
     <mergeCell ref="J33:J34"/>
     <mergeCell ref="K33:K34"/>
     <mergeCell ref="J35:J36"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="K31:K32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Litespeed Toscano 2025.xlsx
+++ b/data/gravel/Litespeed Toscano 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CF8579-7B69-E94B-A874-47D365C1DE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334C6405-5784-EE4F-95B2-43F58F0EA4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="141">
   <si>
     <t>brand</t>
   </si>
@@ -438,6 +438,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -805,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF73"/>
+  <dimension ref="A1:AF79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2740,159 +2758,141 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C49" s="1"/>
+        <v>135</v>
+      </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>137</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53">
-        <v>42</v>
+        <v>139</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>46</v>
-      </c>
-      <c r="B54" s="1"/>
+        <v>140</v>
+      </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>47</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C55" s="1"/>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="B59">
+        <v>42</v>
+      </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>52</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B60" s="1"/>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>54</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>57</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>66</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B65" s="1"/>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>118</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>60</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B69">
-        <v>2399</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>62</v>
-      </c>
-      <c r="B70">
-        <v>4975</v>
+        <v>56</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>66</v>
@@ -2900,27 +2900,70 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
+        <v>59</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>60</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76">
+        <v>4975</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
         <v>132</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>133</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="K31:K32"/>
     <mergeCell ref="J41:J42"/>
     <mergeCell ref="K41:K42"/>
     <mergeCell ref="L29:L30"/>
@@ -2937,6 +2980,11 @@
     <mergeCell ref="J33:J34"/>
     <mergeCell ref="K33:K34"/>
     <mergeCell ref="J35:J36"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="K31:K32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Litespeed Toscano 2025.xlsx
+++ b/data/gravel/Litespeed Toscano 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334C6405-5784-EE4F-95B2-43F58F0EA4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E314BE-9604-3F43-BCF0-7690523016A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="140">
   <si>
     <t>brand</t>
   </si>
@@ -387,9 +387,6 @@
   </si>
   <si>
     <t>188 - 198</t>
-  </si>
-  <si>
-    <t>es</t>
   </si>
   <si>
     <t>rigid</t>
@@ -842,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -866,12 +863,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:32">
       <c r="B6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:32">
@@ -879,13 +876,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>99</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:32">
@@ -1123,10 +1120,10 @@
         <v>97</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q10" s="4" t="s">
         <v>87</v>
@@ -1432,7 +1429,7 @@
         <v>59</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T13" s="5" t="s">
         <v>98</v>
@@ -1531,7 +1528,7 @@
         <v>61</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T14" s="5" t="s">
         <v>98</v>
@@ -1624,7 +1621,7 @@
         <v>108.3</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:32">
@@ -2177,7 +2174,7 @@
         <v>59</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T21" s="5" t="s">
         <v>98</v>
@@ -2270,7 +2267,7 @@
         <v>61</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T22" s="5" t="s">
         <v>98</v>
@@ -2364,7 +2361,7 @@
     </row>
     <row r="25" spans="1:32">
       <c r="A25" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:32">
@@ -2586,10 +2583,10 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" t="s">
         <v>126</v>
-      </c>
-      <c r="B35" t="s">
-        <v>127</v>
       </c>
       <c r="J35" s="6" t="s">
         <v>89</v>
@@ -2603,10 +2600,10 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
+        <v>127</v>
+      </c>
+      <c r="B36" t="s">
         <v>128</v>
-      </c>
-      <c r="B36" t="s">
-        <v>129</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
@@ -2614,24 +2611,24 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>92</v>
@@ -2758,32 +2755,32 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -2903,7 +2900,7 @@
         <v>58</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2951,19 +2948,24 @@
         <v>64</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
+        <v>131</v>
+      </c>
+      <c r="B79" t="s">
         <v>132</v>
-      </c>
-      <c r="B79" t="s">
-        <v>133</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="K31:K32"/>
     <mergeCell ref="J41:J42"/>
     <mergeCell ref="K41:K42"/>
     <mergeCell ref="L29:L30"/>
@@ -2980,11 +2982,6 @@
     <mergeCell ref="J33:J34"/>
     <mergeCell ref="K33:K34"/>
     <mergeCell ref="J35:J36"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="K31:K32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
